--- a/content/02_리서치/2026-06-30_API비용산정_근거_OptionB.xlsx
+++ b/content/02_리서치/2026-06-30_API비용산정_근거_OptionB.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -591,7 +591,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>■ 가정 (Assumptions)</t>
@@ -625,7 +625,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>① 고정 구독 (월 정액)</t>
@@ -790,7 +790,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Max $100/유저 — 개발·디자인 실무자</t>
+          <t>Max $100/유저</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Pro $20/유저 — PM</t>
+          <t>Pro $20/유저</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
+    <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>② 사용량 기반 API — 토큰 기반 (Claude Sonnet)</t>
@@ -966,7 +966,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>③ 사용량 기반 — 이미지 생성 (GPT Image 2, quality: medium)</t>
@@ -1074,7 +1074,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
+    <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>④ 사용량 기반 — 영상 생성 (fal.ai / 1세트 = 1클립)</t>
@@ -1159,21 +1159,21 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>주 2회×4주 / 3~5초 상한 기준</t>
+          <t>1주차~4주차 / BE 주 2회 × 4주 / 3~5초 상한 기준</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>fal.ai Seedance 2.0 — 중간점검 (5초/클립)</t>
+          <t>fal.ai Seedance 2.0 — 2주차 중간점검 (5초/클립)</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
         <v>0.3034</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>5</v>
@@ -1192,24 +1192,24 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>2주차 중간점검 데모 / 720p standard</t>
+          <t>BE 연동 3+품질 3+PM확인 2+리허설 1+데모 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>fal.ai Seedance 2.0 — 최종 출력 (15초/클립, 최대 길이)</t>
+          <t>fal.ai Seedance 2.0 — 3주차 품질 확인 (10초/클립)</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
         <v>0.3034</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E34" s="5">
         <f>C34*D34</f>
@@ -1225,103 +1225,121 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>4주차 최종 발표 2세트 / 720p / 음성 포함</t>
+          <t>BE 품질조정 3+PM검수 2+팀리뷰 1</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>fal.ai Seedance 2.0 — 4주차 최종 출력 (15초/클립, 최대 길이)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="5">
+        <f>C35*D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="7">
+        <f>B35*E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>F35*$B$4</f>
+        <v/>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>BE확인 2+PM검수 2+리허설 1+최종발표 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>영상 소계</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="10">
-        <f>SUM(F32:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="11">
-        <f>F35*$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ★ fal.ai Hard Limit 권장 $50 설정 (Billing &gt; Spend Limit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="10">
+        <f>SUM(F32:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
+        <f>F36*$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ★ fal.ai Hard Limit 권장 $100 설정 (Billing &gt; Spend Limit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>■ 요약</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>① 고정 구독 소계</t>
-        </is>
-      </c>
-      <c r="B40" s="18">
-        <f>D15</f>
-        <v/>
-      </c>
-      <c r="C40" s="19">
-        <f>E15</f>
-        <v/>
-      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>②③④ API/이미지/영상 소계 (B등급)</t>
+          <t>① 고정 구독 소계</t>
         </is>
       </c>
       <c r="B41" s="18">
-        <f>D27+F32+F33+G19</f>
+        <f>D15</f>
         <v/>
       </c>
       <c r="C41" s="19">
-        <f>B41*$B$4</f>
+        <f>E15</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>②③④ API/이미지/영상 소계 (S등급 도전)</t>
+          <t>②③④ API/이미지/영상 소계 (B등급)</t>
         </is>
       </c>
       <c r="B42" s="18">
-        <f>D27+F32+F33+F34+G19+G20</f>
+        <f>D27+F32+F33+F34+G19</f>
         <v/>
       </c>
       <c r="C42" s="19">
@@ -1329,54 +1347,69 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>②③④ API/이미지/영상 소계 (S등급 도전)</t>
+        </is>
+      </c>
+      <c r="B43" s="18">
+        <f>D27+F32+F33+F34+F35+G19+G20</f>
+        <v/>
+      </c>
+      <c r="C43" s="19">
+        <f>B43*$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>★ 총 합계 — B등급</t>
         </is>
       </c>
-      <c r="B43" s="21">
-        <f>D15+B41</f>
-        <v/>
-      </c>
-      <c r="C43" s="22">
-        <f>B43*$B$4</f>
-        <v/>
-      </c>
-      <c r="D43" s="23" t="n"/>
-      <c r="E43" s="23" t="n"/>
-      <c r="F43" s="23" t="n"/>
-      <c r="G43" s="23" t="n"/>
-      <c r="H43" s="23" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="B44" s="21">
+        <f>D15+B42</f>
+        <v/>
+      </c>
+      <c r="C44" s="22">
+        <f>B44*$B$4</f>
+        <v/>
+      </c>
+      <c r="D44" s="23" t="n"/>
+      <c r="E44" s="23" t="n"/>
+      <c r="F44" s="23" t="n"/>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="23" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
         <is>
           <t>★ 총 합계 — S등급 (권장)</t>
         </is>
       </c>
-      <c r="B44" s="25">
-        <f>D15+B42</f>
-        <v/>
-      </c>
-      <c r="C44" s="26">
-        <f>B44*$B$4</f>
-        <v/>
-      </c>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
-      <c r="H44" s="27" t="n"/>
+      <c r="B45" s="25">
+        <f>D15+B43</f>
+        <v/>
+      </c>
+      <c r="C45" s="26">
+        <f>B45*$B$4</f>
+        <v/>
+      </c>
+      <c r="D45" s="27" t="n"/>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="27" t="n"/>
+      <c r="H45" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A17:H17"/>
